--- a/accounts_result.xlsx
+++ b/accounts_result.xlsx
@@ -489,40 +489,40 @@
     </row>
     <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>santiago.ramirez@manilamedical.ph</v>
+        <v>lorenzo.guerrero@quezoncityhospital.ph</v>
       </c>
       <c r="B2" t="str">
-        <v>MedSantiago2345@Manila</v>
+        <v>MedLorenzo5678@QuezonCity</v>
       </c>
       <c r="C2" t="str">
-        <v>Santiago</v>
+        <v>Lorenzo</v>
       </c>
       <c r="D2" t="str">
-        <v>Ramirez</v>
+        <v>Guerrero</v>
       </c>
       <c r="E2" t="str">
-        <v>Manila Medical Center</v>
+        <v>Quezon City General Hospital</v>
       </c>
       <c r="F2" t="str">
         <v>1 person</v>
       </c>
       <c r="G2" t="str">
-        <v>+63289882345</v>
+        <v>+63287655678</v>
       </c>
       <c r="H2" t="str">
-        <v>Cardiothoracic Surgeon</v>
+        <v>Cardiovascular Surgeon</v>
       </c>
       <c r="I2" t="str">
-        <v>1945 Taft Avenue</v>
+        <v>1101 Epifanio de los Santos Avenue, Diliman</v>
       </c>
       <c r="J2" t="str">
-        <v>Manila</v>
+        <v>Quezon City</v>
       </c>
       <c r="K2" t="str">
         <v>Metro Manila</v>
       </c>
       <c r="L2" t="str">
-        <v>1004</v>
+        <v>1105</v>
       </c>
       <c r="M2" t="str">
         <v>Philippines</v>
@@ -549,39 +549,39 @@
         <v/>
       </c>
       <c r="U2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step: Filling basic info - Error: locator.waitFor: Timeout 15000ms exceeded.
+        <v xml:space="preserve">Step: Finishing trial setup - Error: locator.waitFor: Target page, context or browser has been closed
 Call log:
-_x001b_[2m  - waiting for locator('div[role="combobox"][id*="region" i], div[role="combobox"][id*="state" i], select[id*="region" i]').first() to be visible_x001b_[22m
+_x001b_[2m  - waiting for locator('button[id*="Next" i], button[data-testid*="Next" i], button[data-bi-id*="Next" i], a[data-bi-id*="Next" i], button:has-text("Next"), a:has-text("Next")').first() to be visible_x001b_[22m
 </v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>isabella.cruz@cebutech.ph</v>
+        <v>carmela.santos@cebubiotech.ph</v>
       </c>
       <c r="B3" t="str">
-        <v>TechIsabella6789@Cebu</v>
+        <v>BioCarmela9012@Cebu</v>
       </c>
       <c r="C3" t="str">
-        <v>Isabella</v>
+        <v>Carmela</v>
       </c>
       <c r="D3" t="str">
-        <v>Cruz</v>
+        <v>Santos</v>
       </c>
       <c r="E3" t="str">
-        <v>Cebu Technology Hub</v>
+        <v>Cebu Biotech Research Center</v>
       </c>
       <c r="F3" t="str">
         <v>1 person</v>
       </c>
       <c r="G3" t="str">
-        <v>+63322656789</v>
+        <v>+63323219012</v>
       </c>
       <c r="H3" t="str">
-        <v>Software Development Manager</v>
+        <v>Molecular Biologist</v>
       </c>
       <c r="I3" t="str">
-        <v>125 Archbishop Reyes Avenue</v>
+        <v>205 M.J. Cuenco Avenue</v>
       </c>
       <c r="J3" t="str">
         <v>Cebu City</v>
@@ -617,48 +617,48 @@
         <v/>
       </c>
       <c r="U3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step: Filling basic info - Error: locator.waitFor: Timeout 15000ms exceeded.
+        <v xml:space="preserve">Step: Finishing trial setup - Error: locator.waitFor: Target page, context or browser has been closed
 Call log:
-_x001b_[2m  - waiting for locator('div[role="combobox"][id*="region" i], div[role="combobox"][id*="state" i], select[id*="region" i]').first() to be visible_x001b_[22m
+_x001b_[2m  - waiting for locator('button[id*="Next" i], button[data-testid*="Next" i], button[data-bi-id*="Next" i], a[data-bi-id*="Next" i], button:has-text("Next"), a:has-text("Next")').first() to be visible_x001b_[22m
 </v>
       </c>
     </row>
-    <row r="4" xml:space="preserve">
+    <row r="4">
       <c r="A4" t="str">
-        <v>mateo.santos@davaoresearch.ph</v>
+        <v>vicente.manalo@makaticapital.ph</v>
       </c>
       <c r="B4" t="str">
-        <v>BioMateo9012@Davao</v>
+        <v>FinVicente2345@Makati</v>
       </c>
       <c r="C4" t="str">
-        <v>Mateo</v>
+        <v>Vicente</v>
       </c>
       <c r="D4" t="str">
-        <v>Santos</v>
+        <v>Manalo</v>
       </c>
       <c r="E4" t="str">
-        <v>Davao Biotech Research Institute</v>
+        <v>Makati Capital Investments</v>
       </c>
       <c r="F4" t="str">
         <v>1 person</v>
       </c>
       <c r="G4" t="str">
-        <v>+63823219012</v>
+        <v>+63288452345</v>
       </c>
       <c r="H4" t="str">
-        <v>Molecular Biologist</v>
+        <v>Financial Portfolio Manager</v>
       </c>
       <c r="I4" t="str">
-        <v>150 University Avenue</v>
+        <v>122 Ayala Avenue</v>
       </c>
       <c r="J4" t="str">
-        <v>Davao City</v>
+        <v>Makati</v>
       </c>
       <c r="K4" t="str">
-        <v>Davao del Sur</v>
+        <v>Metro Manila</v>
       </c>
       <c r="L4" t="str">
-        <v>8000</v>
+        <v>1226</v>
       </c>
       <c r="M4" t="str">
         <v>Philippines</v>
@@ -676,57 +676,54 @@
         <v>29</v>
       </c>
       <c r="R4" t="str">
-        <v>FAILED</v>
+        <v>SUCCESS</v>
       </c>
       <c r="S4" t="str">
-        <v/>
+        <v>vicentemanalo@makaticapitalinvestments.onmicrosoft.com</v>
       </c>
       <c r="T4" t="str">
-        <v/>
-      </c>
-      <c r="U4" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step: Filling basic info - Error: locator.waitFor: Timeout 15000ms exceeded.
-Call log:
-_x001b_[2m  - waiting for locator('div[role="combobox"][id*="region" i], div[role="combobox"][id*="state" i], select[id*="region" i]').first() to be visible_x001b_[22m
-</v>
+        <v>FinVicente2345@Makati</v>
+      </c>
+      <c r="U4" t="str">
+        <v>Completed successfully</v>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
+    <row r="5">
       <c r="A5" t="str">
-        <v>gabriela.reyes@quezoncityedu.ph</v>
+        <v>socorro.ramos@davaoeducation.ph</v>
       </c>
       <c r="B5" t="str">
-        <v>EduGabriela3456@QuezonCity</v>
+        <v>EduSocorro6789@Davao</v>
       </c>
       <c r="C5" t="str">
-        <v>Gabriela</v>
+        <v>Socorro</v>
       </c>
       <c r="D5" t="str">
-        <v>Reyes</v>
+        <v>Ramos</v>
       </c>
       <c r="E5" t="str">
-        <v>Quezon City University</v>
+        <v>Davao City University</v>
       </c>
       <c r="F5" t="str">
         <v>1 person</v>
       </c>
       <c r="G5" t="str">
-        <v>+63287653456</v>
+        <v>+63823216789</v>
       </c>
       <c r="H5" t="str">
-        <v>Academic Dean</v>
+        <v>Dean of Liberal Arts</v>
       </c>
       <c r="I5" t="str">
-        <v>1101 Commonwealth Avenue</v>
+        <v>150 Jacinto Street</v>
       </c>
       <c r="J5" t="str">
-        <v>Quezon City</v>
+        <v>Davao City</v>
       </c>
       <c r="K5" t="str">
-        <v>Metro Manila</v>
+        <v>Davao del Sur</v>
       </c>
       <c r="L5" t="str">
-        <v>1105</v>
+        <v>8000</v>
       </c>
       <c r="M5" t="str">
         <v>Philippines</v>
@@ -744,57 +741,54 @@
         <v>29</v>
       </c>
       <c r="R5" t="str">
-        <v>FAILED</v>
+        <v>SUCCESS</v>
       </c>
       <c r="S5" t="str">
-        <v/>
+        <v>socorroramos@davaocityuniversity.onmicrosoft.com</v>
       </c>
       <c r="T5" t="str">
-        <v/>
-      </c>
-      <c r="U5" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step: Filling basic info - Error: locator.waitFor: Timeout 15000ms exceeded.
-Call log:
-_x001b_[2m  - waiting for locator('div[role="combobox"][id*="region" i], div[role="combobox"][id*="state" i], select[id*="region" i]').first() to be visible_x001b_[22m
-</v>
+        <v>EduSocorro6789@Davao</v>
+      </c>
+      <c r="U5" t="str">
+        <v>Completed successfully</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
       <c r="A6" t="str">
-        <v>alejandro.villanueva@makatienergy.ph</v>
+        <v>rolando.mercado@manilaenergy.ph</v>
       </c>
       <c r="B6" t="str">
-        <v>EnergyAlejandro7890@Makati</v>
+        <v>EnergyRolando3456@Manila</v>
       </c>
       <c r="C6" t="str">
-        <v>Alejandro</v>
+        <v>Rolando</v>
       </c>
       <c r="D6" t="str">
-        <v>Villanueva</v>
+        <v>Mercado</v>
       </c>
       <c r="E6" t="str">
-        <v>Makati Energy Solutions</v>
+        <v>Manila Energy Corporation</v>
       </c>
       <c r="F6" t="str">
         <v>1 person</v>
       </c>
       <c r="G6" t="str">
-        <v>+63288457890</v>
+        <v>+63285233456</v>
       </c>
       <c r="H6" t="str">
-        <v>Renewable Energy Engineer</v>
+        <v>Power Systems Engineer</v>
       </c>
       <c r="I6" t="str">
-        <v>122 Ayala Avenue</v>
+        <v>123 Roxas Boulevard</v>
       </c>
       <c r="J6" t="str">
-        <v>Makati</v>
+        <v>Manila</v>
       </c>
       <c r="K6" t="str">
         <v>Metro Manila</v>
       </c>
       <c r="L6" t="str">
-        <v>1226</v>
+        <v>1004</v>
       </c>
       <c r="M6" t="str">
         <v>Philippines</v>
@@ -821,9 +815,9 @@
         <v/>
       </c>
       <c r="U6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step: Filling basic info - Error: locator.waitFor: Timeout 15000ms exceeded.
+        <v xml:space="preserve">Step: Finishing trial setup - Error: locator.waitFor: Target page, context or browser has been closed
 Call log:
-_x001b_[2m  - waiting for locator('div[role="combobox"][id*="region" i], div[role="combobox"][id*="state" i], select[id*="region" i]').first() to be visible_x001b_[22m
+_x001b_[2m  - waiting for locator('button[id*="Next" i], button[data-testid*="Next" i], button[data-bi-id*="Next" i], a[data-bi-id*="Next" i], button:has-text("Next"), a:has-text("Next")').first() to be visible_x001b_[22m
 </v>
       </c>
     </row>

--- a/accounts_result.xlsx
+++ b/accounts_result.xlsx
@@ -487,42 +487,42 @@
         <v>Log</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
+    <row r="2">
       <c r="A2" t="str">
-        <v>lorenzo.guerrero@quezoncityhospital.ph</v>
+        <v>ferdinand.delacruz@manilamedical.ph</v>
       </c>
       <c r="B2" t="str">
-        <v>MedLorenzo5678@QuezonCity</v>
+        <v>MedFerdinand2389@Manila</v>
       </c>
       <c r="C2" t="str">
-        <v>Lorenzo</v>
+        <v>Ferdinand</v>
       </c>
       <c r="D2" t="str">
-        <v>Guerrero</v>
+        <v>Dela Cruz</v>
       </c>
       <c r="E2" t="str">
-        <v>Quezon City General Hospital</v>
+        <v>Manila Medical Specialists Hospital</v>
       </c>
       <c r="F2" t="str">
         <v>1 person</v>
       </c>
       <c r="G2" t="str">
-        <v>+63287655678</v>
+        <v>+63285232389</v>
       </c>
       <c r="H2" t="str">
-        <v>Cardiovascular Surgeon</v>
+        <v>Neurosurgeon</v>
       </c>
       <c r="I2" t="str">
-        <v>1101 Epifanio de los Santos Avenue, Diliman</v>
+        <v>1780 Taft Avenue</v>
       </c>
       <c r="J2" t="str">
-        <v>Quezon City</v>
+        <v>Manila</v>
       </c>
       <c r="K2" t="str">
         <v>Metro Manila</v>
       </c>
       <c r="L2" t="str">
-        <v>1105</v>
+        <v>1004</v>
       </c>
       <c r="M2" t="str">
         <v>Philippines</v>
@@ -548,173 +548,173 @@
       <c r="T2" t="str">
         <v/>
       </c>
-      <c r="U2" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step: Finishing trial setup - Error: locator.waitFor: Target page, context or browser has been closed
+      <c r="U2" t="str">
+        <v>Step: Building cart - Error: page.waitForTimeout: Target page, context or browser has been closed</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>consuelo.villanueva@ceburesearch.ph</v>
+      </c>
+      <c r="B3" t="str">
+        <v>BioConsuelo6712@Cebu</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Consuelo</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Villanueva</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Cebu Institute for Molecular Research</v>
+      </c>
+      <c r="F3" t="str">
+        <v>1 person</v>
+      </c>
+      <c r="G3" t="str">
+        <v>+63322516712</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Biochemistry Researcher</v>
+      </c>
+      <c r="I3" t="str">
+        <v>45 Gorordo Avenue</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Cebu City</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Cebu</v>
+      </c>
+      <c r="L3" t="str">
+        <v>6000</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Philippines</v>
+      </c>
+      <c r="N3" t="str">
+        <v>4983920020166734</v>
+      </c>
+      <c r="O3" t="str">
+        <v>068</v>
+      </c>
+      <c r="P3" t="str">
+        <v>03</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>29</v>
+      </c>
+      <c r="R3" t="str">
+        <v>FAILED</v>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step: Finishing trial setup - Error: locator.waitFor: Timeout 120000ms exceeded.
 Call log:
 _x001b_[2m  - waiting for locator('button[id*="Next" i], button[data-testid*="Next" i], button[data-bi-id*="Next" i], a[data-bi-id*="Next" i], button:has-text("Next"), a:has-text("Next")').first() to be visible_x001b_[22m
 </v>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
-      <c r="A3" t="str">
-        <v>carmela.santos@cebubiotech.ph</v>
-      </c>
-      <c r="B3" t="str">
-        <v>BioCarmela9012@Cebu</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Carmela</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Santos</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Cebu Biotech Research Center</v>
-      </c>
-      <c r="F3" t="str">
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>anastacio.lorenzo@makatiinvest.ph</v>
+      </c>
+      <c r="B4" t="str">
+        <v>FinAnastacio9053@Makati</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Anastacio</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Lorenzo</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Makati Investment Management Group</v>
+      </c>
+      <c r="F4" t="str">
         <v>1 person</v>
       </c>
-      <c r="G3" t="str">
-        <v>+63323219012</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Molecular Biologist</v>
-      </c>
-      <c r="I3" t="str">
-        <v>205 M.J. Cuenco Avenue</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Cebu City</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Cebu</v>
-      </c>
-      <c r="L3" t="str">
-        <v>6000</v>
-      </c>
-      <c r="M3" t="str">
+      <c r="G4" t="str">
+        <v>+63288129053</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Wealth Management Advisor</v>
+      </c>
+      <c r="I4" t="str">
+        <v>8761 Paseo de Roxas</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Makati</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Metro Manila</v>
+      </c>
+      <c r="L4" t="str">
+        <v>1226</v>
+      </c>
+      <c r="M4" t="str">
         <v>Philippines</v>
       </c>
-      <c r="N3" t="str">
-        <v>4983920020166734</v>
-      </c>
-      <c r="O3" t="str">
-        <v>068</v>
-      </c>
-      <c r="P3" t="str">
+      <c r="N4" t="str">
+        <v>4983920028370205</v>
+      </c>
+      <c r="O4" t="str">
+        <v>402</v>
+      </c>
+      <c r="P4" t="str">
         <v>03</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="Q4" t="str">
         <v>29</v>
       </c>
-      <c r="R3" t="str">
+      <c r="R4" t="str">
         <v>FAILED</v>
       </c>
-      <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
-        <v/>
-      </c>
-      <c r="U3" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step: Finishing trial setup - Error: locator.waitFor: Target page, context or browser has been closed
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step: Finishing trial setup - Error: locator.waitFor: Timeout 120000ms exceeded.
 Call log:
 _x001b_[2m  - waiting for locator('button[id*="Next" i], button[data-testid*="Next" i], button[data-bi-id*="Next" i], a[data-bi-id*="Next" i], button:has-text("Next"), a:has-text("Next")').first() to be visible_x001b_[22m
 </v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>vicente.manalo@makaticapital.ph</v>
-      </c>
-      <c r="B4" t="str">
-        <v>FinVicente2345@Makati</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Vicente</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Manalo</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Makati Capital Investments</v>
-      </c>
-      <c r="F4" t="str">
-        <v>1 person</v>
-      </c>
-      <c r="G4" t="str">
-        <v>+63288452345</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Financial Portfolio Manager</v>
-      </c>
-      <c r="I4" t="str">
-        <v>122 Ayala Avenue</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Makati</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Metro Manila</v>
-      </c>
-      <c r="L4" t="str">
-        <v>1226</v>
-      </c>
-      <c r="M4" t="str">
-        <v>Philippines</v>
-      </c>
-      <c r="N4" t="str">
-        <v>4983920028370205</v>
-      </c>
-      <c r="O4" t="str">
-        <v>402</v>
-      </c>
-      <c r="P4" t="str">
-        <v>03</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>29</v>
-      </c>
-      <c r="R4" t="str">
-        <v>SUCCESS</v>
-      </c>
-      <c r="S4" t="str">
-        <v>vicentemanalo@makaticapitalinvestments.onmicrosoft.com</v>
-      </c>
-      <c r="T4" t="str">
-        <v>FinVicente2345@Makati</v>
-      </c>
-      <c r="U4" t="str">
-        <v>Completed successfully</v>
-      </c>
-    </row>
-    <row r="5">
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
-        <v>socorro.ramos@davaoeducation.ph</v>
+        <v>remedios.gutierrez@davaouniversity.ph</v>
       </c>
       <c r="B5" t="str">
-        <v>EduSocorro6789@Davao</v>
+        <v>EduRemedios4428@Davao</v>
       </c>
       <c r="C5" t="str">
-        <v>Socorro</v>
+        <v>Remedios</v>
       </c>
       <c r="D5" t="str">
-        <v>Ramos</v>
+        <v>Gutierrez</v>
       </c>
       <c r="E5" t="str">
-        <v>Davao City University</v>
+        <v>Davao University - College of Education</v>
       </c>
       <c r="F5" t="str">
         <v>1 person</v>
       </c>
       <c r="G5" t="str">
-        <v>+63823216789</v>
+        <v>+63823214428</v>
       </c>
       <c r="H5" t="str">
-        <v>Dean of Liberal Arts</v>
+        <v>Professor of Linguistics</v>
       </c>
       <c r="I5" t="str">
-        <v>150 Jacinto Street</v>
+        <v>225 MacArthur Highway</v>
       </c>
       <c r="J5" t="str">
         <v>Davao City</v>
@@ -741,54 +741,57 @@
         <v>29</v>
       </c>
       <c r="R5" t="str">
-        <v>SUCCESS</v>
+        <v>FAILED</v>
       </c>
       <c r="S5" t="str">
-        <v>socorroramos@davaocityuniversity.onmicrosoft.com</v>
+        <v/>
       </c>
       <c r="T5" t="str">
-        <v>EduSocorro6789@Davao</v>
-      </c>
-      <c r="U5" t="str">
-        <v>Completed successfully</v>
+        <v/>
+      </c>
+      <c r="U5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step: Filling password - Error: locator.waitFor: Timeout 30000ms exceeded.
+Call log:
+_x001b_[2m  - waiting for locator('input[type="password"]:not([id*="retype" i]):not([id*="confirm" i]):not([data-testid*="cpwd" i])').first() to be visible_x001b_[22m
+</v>
       </c>
     </row>
     <row r="6" xml:space="preserve">
       <c r="A6" t="str">
-        <v>rolando.mercado@manilaenergy.ph</v>
+        <v>gregorio.macapagal@quezonpower.ph</v>
       </c>
       <c r="B6" t="str">
-        <v>EnergyRolando3456@Manila</v>
+        <v>EnergyGregorio5176@Quezon</v>
       </c>
       <c r="C6" t="str">
-        <v>Rolando</v>
+        <v>Gregorio</v>
       </c>
       <c r="D6" t="str">
-        <v>Mercado</v>
+        <v>Macapagal</v>
       </c>
       <c r="E6" t="str">
-        <v>Manila Energy Corporation</v>
+        <v>Quezon Power Generation Corp</v>
       </c>
       <c r="F6" t="str">
         <v>1 person</v>
       </c>
       <c r="G6" t="str">
-        <v>+63285233456</v>
+        <v>+63289215176</v>
       </c>
       <c r="H6" t="str">
-        <v>Power Systems Engineer</v>
+        <v>Senior Power Plant Engineer</v>
       </c>
       <c r="I6" t="str">
-        <v>123 Roxas Boulevard</v>
+        <v>88 Commonwealth Avenue</v>
       </c>
       <c r="J6" t="str">
-        <v>Manila</v>
+        <v>Quezon City</v>
       </c>
       <c r="K6" t="str">
         <v>Metro Manila</v>
       </c>
       <c r="L6" t="str">
-        <v>1004</v>
+        <v>1121</v>
       </c>
       <c r="M6" t="str">
         <v>Philippines</v>
@@ -815,9 +818,9 @@
         <v/>
       </c>
       <c r="U6" t="str" xml:space="preserve">
-        <v xml:space="preserve">Step: Finishing trial setup - Error: locator.waitFor: Target page, context or browser has been closed
+        <v xml:space="preserve">Step: Confirming email email - Error: locator.waitFor: Timeout 150000ms exceeded.
 Call log:
-_x001b_[2m  - waiting for locator('button[id*="Next" i], button[data-testid*="Next" i], button[data-bi-id*="Next" i], a[data-bi-id*="Next" i], button:has-text("Next"), a:has-text("Next")').first() to be visible_x001b_[22m
+_x001b_[2m  - waiting for locator('button[id*="Setup" i], button[data-testid*="Setup" i], button[data-bi-id*="Setup" i], a[data-bi-id*="Setup" i], button:has-text("Setup"), a:has-text("Setup")').first() to be visible_x001b_[22m
 </v>
       </c>
     </row>

--- a/accounts_result.xlsx
+++ b/accounts_result.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <cols>
     <col min="1" max="1" width="45.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -426,9 +426,31 @@
         <v>2026-03-10</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>IloiloBiomedicalCenter.onmicrosoft.com</v>
+      </c>
+      <c r="B3" t="str">
+        <v>BioBeatrice4572@Iloilo</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-03-11</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>PasigHealthResearchUnit.onmicrosoft.com</v>
+      </c>
+      <c r="B4" t="str">
+        <v>HealthClarisse4574@Pasig</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-03-11</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
 </file>